--- a/financial_models/opportunities/not_monitored/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/not_monitored/0341.HK_Valuation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\not_monitored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD821A5-6D16-4613-A61B-FD94FC0C2D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73697ABE-4E25-4A13-BDC9-A37B7DB6CAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/not_monitored/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/not_monitored/0341.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\not_monitored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73697ABE-4E25-4A13-BDC9-A37B7DB6CAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D56DF43-4993-4D9B-A2C2-563387362E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="464">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2443,9 +2443,6 @@
   </si>
   <si>
     <t>LT AR and Prepayments</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>大家樂集團</t>
@@ -3891,29 +3888,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4241,7 +4238,7 @@
         <v>353</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4272,7 +4269,7 @@
         <v>315</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4319,10 +4316,10 @@
         <v>416</v>
       </c>
       <c r="C11" s="49" t="s">
+        <v>456</v>
+      </c>
+      <c r="D11" s="49" t="s">
         <v>457</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>458</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4389,13 +4386,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4416,7 +4413,7 @@
         <v>438</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4424,7 +4421,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4437,7 +4434,7 @@
         <v>433</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4445,7 +4442,7 @@
         <v>434</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -4595,22 +4592,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4619,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4645,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4680,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4702,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4772,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4794,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4816,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4969,22 +4966,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5025,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5077,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5096,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5224,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5269,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5418,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5437,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5785,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5828,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5842,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5881,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5897,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6555,7 +6552,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12380,7 +12377,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12712,7 +12709,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">

--- a/financial_models/opportunities/not_monitored/0341.HK_Valuation.xlsx
+++ b/financial_models/opportunities/not_monitored/0341.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\not_monitored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2052FE62-2947-4162-80AC-3A35E9D15FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DD469D-6D00-49F7-83E6-8944FCC90E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3889,29 +3889,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4385,13 +4385,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4467,14 +4467,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>0.48595173431638328</v>
+        <v>7.1432431801746707</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>398</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.43709190940773135</v>
+        <v>6.6775026397374759E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>0.87586312424585011</v>
+        <v>3.5816666890919757</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>1.0296072879699882</v>
+        <v>4.4381405082494316</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>1.4166029491791647</v>
+        <v>6.7013755367692536</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>1.3066233531657026</v>
+        <v>6.0451519082648151</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4591,22 +4591,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>337</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4618,13 +4618,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
-        <v>290125.03743286617</v>
+        <v>644526.70500000007</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4644,13 +4644,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4679,13 +4679,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4701,13 +4701,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4771,13 +4771,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-30691.656176422919</v>
+        <v>-89167.931325000012</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4793,7 +4793,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>336</v>
       </c>
       <c r="C61" s="362"/>
@@ -4815,22 +4815,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>152714.08977285403</v>
+        <v>448639.48219141085</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.7939239762176669E-2</v>
+        <v>0.11145691210912964</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>1.5191893134751204</v>
+        <v>0.51712259488793089</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>6.77697372107431E-2</v>
+        <v>0.19689023097303349</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>2.2689295427486551E-2</v>
+        <v>6.5918812750317815E-2</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
@@ -4965,22 +4965,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5024,22 +5024,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.2912290493688263</v>
+        <v>9.6688871254669966</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5076,13 +5076,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5095,13 +5095,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>342</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>7.3565177927598588</v>
+        <v>3.3114376540844801</v>
       </c>
     </row>
     <row r="107" spans="2:6">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>375298.22285273892</v>
+        <v>404831.69515000004</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.64706140216224828</v>
+        <v>0.69798082791951899</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5223,13 +5223,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>0.36792251927912745</v>
+        <v>6.7965000211345696</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5268,13 +5268,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>0.81 HKD</v>
+        <v>8.11 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>0.53 HKD</v>
+        <v>7.27 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>0.47 HKD</v>
+        <v>7.11 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>0.42 HKD</v>
+        <v>6.95 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>0.37 HKD</v>
+        <v>6.8 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>0.48595173431638328</v>
+        <v>7.1432431801746707</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5417,13 +5417,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>369</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5436,22 +5436,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>367</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>0.19751124699136643</v>
+        <v>2.9033148118374918</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>0.87586312424585011</v>
+        <v>3.5816666890919757</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>-0.80236649526105297</v>
+        <v>0.49859376213979112</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>0.24880728796998824</v>
+        <v>3.6573405082494315</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>1.0296072879699882</v>
+        <v>4.4381405082494316</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>-1.1187439312638672</v>
+        <v>0.3786939074723048</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>0.38576415428001259</v>
+        <v>5.6705367418701016</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>1.4166029491791647</v>
+        <v>6.7013755367692536</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>-1.9151103888372432</v>
+        <v>6.1858126940403602E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>0.34589084587707208</v>
+        <v>5.0844194009761843</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>1.3066233531657026</v>
+        <v>6.0451519082648151</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>-1.6429002582483059</v>
+        <v>0.15665119099582092</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5784,13 +5784,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>375</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5827,13 +5827,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>380</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5841,22 +5841,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>381</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>382</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5880,6 +5880,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5896,17 +5907,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
-        <v>7.3565177927598588</v>
+        <v>3.3114376540844801</v>
       </c>
       <c r="D50" s="95">
         <f>G31/Normalized_FCF!G8</f>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
-        <v>6.4677617909509572E-2</v>
+        <v>0.14368443457111585</v>
       </c>
       <c r="D54" s="92">
         <f>Normalized_FCF!G8/G35</f>
@@ -9469,7 +9469,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>375298.22285273892</v>
+        <v>404831.69515000004</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-678334.77714726108</v>
+        <v>-648801.30484999996</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>349</v>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.5532640157873914</v>
+        <v>1.6239686821277206</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>317</v>
@@ -9569,7 +9569,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>678334.77714726108</v>
+        <v>648801.30484999996</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>350</v>
@@ -9701,11 +9701,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>375298.22285273892</v>
+        <v>404831.69515000004</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.64706140216224828</v>
+        <v>0.69798082791951899</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9735,11 +9735,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-1695529.577147261</v>
+        <v>-1665996.10485</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-2.9233065300896985</v>
+        <v>-2.8723871043324278</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="C5" s="328">
         <f>C25</f>
-        <v>-7422358.7125671338</v>
+        <v>-7050401.0449999999</v>
       </c>
       <c r="E5" s="268"/>
       <c r="G5" s="333">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="C6" s="329">
         <f>C4+C5</f>
-        <v>775782.03743286617</v>
+        <v>1147739.7050000001</v>
       </c>
       <c r="E6" s="268"/>
       <c r="G6" s="329">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="C7" s="328">
         <f>C35</f>
-        <v>-485657</v>
+        <v>-503213</v>
       </c>
       <c r="E7" s="268"/>
       <c r="G7" s="328">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
-        <v>290125.03743286617</v>
+        <v>644526.70500000007</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>186010.03743286617</v>
+        <v>540411.70500000007</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-30691.656176422919</v>
+        <v>-89167.931325000012</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>152714.08977285403</v>
+        <v>448639.48219141085</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>152714.08977285403</v>
+        <v>448639.48219141085</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
@@ -10769,7 +10769,7 @@
       </c>
       <c r="C23" s="337">
         <f>-C4*C28</f>
-        <v>-7422358.7125671338</v>
+        <v>-7050401.0449999999</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="C25" s="329">
         <f>C23+C24</f>
-        <v>-7422358.7125671338</v>
+        <v>-7050401.0449999999</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
@@ -10950,8 +10950,7 @@
         <v>43</v>
       </c>
       <c r="C28" s="63">
-        <f>AVERAGE(G28:J28)</f>
-        <v>0.90537097848279002</v>
+        <v>0.86</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
@@ -11070,7 +11069,7 @@
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
-        <v>0.90537097848279002</v>
+        <v>0.86</v>
       </c>
       <c r="E30" s="268"/>
       <c r="G30" s="30">
@@ -11135,8 +11134,8 @@
         <v>173</v>
       </c>
       <c r="C33" s="340">
-        <f>AVERAGE(G33:J33)</f>
-        <v>-485657</v>
+        <f>H33</f>
+        <v>-503213</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>331</v>
@@ -11252,7 +11251,7 @@
       </c>
       <c r="C35" s="329">
         <f>C33+C34</f>
-        <v>-485657</v>
+        <v>-503213</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
@@ -11321,7 +11320,7 @@
       </c>
       <c r="C38" s="23">
         <f>ABS(C33/$C$4)</f>
-        <v>5.9239895338464396E-2</v>
+        <v>6.1381356498423134E-2</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="265"/>
@@ -11436,7 +11435,7 @@
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
-        <v>5.9239895338464396E-2</v>
+        <v>6.1381356498423134E-2</v>
       </c>
       <c r="E40" s="268"/>
       <c r="G40" s="30">
@@ -11882,7 +11881,7 @@
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>2.7865825042776371</v>
+        <v>6.1905268693271873</v>
       </c>
       <c r="E55" s="268"/>
       <c r="G55" s="42">
@@ -12445,7 +12444,7 @@
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
-        <v>0.90537097848279002</v>
+        <v>0.86</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="265"/>
@@ -12502,7 +12501,7 @@
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
-        <v>9.4629021517210005E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="265"/>
@@ -12559,7 +12558,7 @@
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
-        <v>5.9239895338464396E-2</v>
+        <v>6.1381356498423134E-2</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="265"/>
@@ -12616,7 +12615,7 @@
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
-        <v>3.5389126178745609E-2</v>
+        <v>7.8618643501576879E-2</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="265"/>
@@ -12903,7 +12902,7 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>2.2689295427486551E-2</v>
+        <v>6.5918812750317815E-2</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
@@ -12960,7 +12959,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.743733745535281E-3</v>
+        <v>1.087660410380244E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -13075,7 +13074,7 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>1.8627893132092666E-2</v>
+        <v>5.4724540096656775E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
@@ -13182,7 +13181,7 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>1.8627893132092666E-2</v>
+        <v>5.4724540096656775E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
@@ -13362,7 +13361,7 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>1.5191893134751204</v>
+        <v>0.51712259488793089</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
@@ -13575,7 +13574,7 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>-0.36741392555317287</v>
+        <v>0.83784124646740166</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
@@ -14294,7 +14293,7 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>2.2689295427486551E-2</v>
+        <v>6.5918812750317815E-2</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
@@ -14459,7 +14458,7 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>6.77697372107431E-2</v>
+        <v>0.19689023097303349</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
@@ -14580,7 +14579,7 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.26329832394950609</v>
+        <v>0.7735109700373598</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
@@ -14637,7 +14636,7 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.7939239762176669E-2</v>
+        <v>0.11145691210912964</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
@@ -15480,7 +15479,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>152714.08977285403</v>
+        <v>448639.48219141085</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15512,7 +15511,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1908926.1221606752</v>
+        <v>5607993.5273926351</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15546,7 +15545,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>375298.22285273892</v>
+        <v>404831.69515000004</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15578,7 +15577,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>213396.54501341417</v>
+        <v>3941997.4225426354</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15606,7 +15605,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>0.36792251927912745</v>
+        <v>6.7965000211345696</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15659,7 +15658,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>0.49438996007807068</v>
+        <v>7.1680327804137081</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15694,7 +15693,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>156341.44940826172</v>
+        <v>459295.84501275804</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -15706,7 +15705,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>144760.60130394602</v>
+        <v>425273.93056736852</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15716,7 +15715,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>160054.96833613649</v>
+        <v>470205.32436327363</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -15728,7 +15727,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>137221.33773674251</v>
+        <v>403125.27808922634</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15738,7 +15737,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>163856.69306535108</v>
+        <v>481373.93242351233</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -15750,7 +15749,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>130074.72586222173</v>
+        <v>382130.1475444485</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15770,7 +15769,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>167748.71871472432</v>
+        <v>492807.82417906466</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -15782,7 +15781,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>123300.31602367747</v>
+        <v>362228.46246327832</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15802,7 +15801,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>171733.19016763484</v>
+        <v>504513.30081255065</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -15814,7 +15813,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>116878.7236010944</v>
+        <v>343363.27521305729</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16454,7 +16453,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1954268.1176032715</v>
+        <v>5741198.062659475</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16466,7 +16465,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>1330042.0433395689</v>
+        <v>3907362.9322887748</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16477,7 +16476,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>1982277.747867251</v>
+        <v>5823484.0261661541</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16498,7 +16497,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>1982277.747867251</v>
+        <v>5823484.0261661541</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16528,19 +16527,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1908926.122160675</v>
+        <v>5607993.5273926342</v>
       </c>
       <c r="C56" s="123">
-        <v>1939496.4778838088</v>
+        <v>5697802.3235713867</v>
       </c>
       <c r="D56" s="123">
-        <v>1970518.0715778847</v>
+        <v>5788936.7549284641</v>
       </c>
       <c r="E56" s="123">
-        <v>2002000.7897348444</v>
+        <v>5881425.8657428287</v>
       </c>
       <c r="F56" s="123">
-        <v>2033954.6730024912</v>
+        <v>5975299.1531685349</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16549,19 +16548,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>1908926.1221606745</v>
+        <v>5607993.5273926333</v>
       </c>
       <c r="C57" s="123">
-        <v>1969088.7804157054</v>
+        <v>5784737.820515438</v>
       </c>
       <c r="D57" s="123">
-        <v>2032166.7374474457</v>
+        <v>5970046.6025833171</v>
       </c>
       <c r="E57" s="123">
-        <v>2098330.3616265729</v>
+        <v>6164420.3773658648</v>
       </c>
       <c r="F57" s="123">
-        <v>2167759.3992531775</v>
+        <v>6368387.1988698822</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16570,19 +16569,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>1908926.1221606743</v>
+        <v>5607993.5273926333</v>
       </c>
       <c r="C58" s="341">
-        <v>2004806.9337375849</v>
+        <v>5889669.6826310828</v>
       </c>
       <c r="D58" s="123">
-        <v>2108474.055034298</v>
+        <v>6194220.2561113006</v>
       </c>
       <c r="E58" s="123">
-        <v>2220665.833747291</v>
+        <v>6523814.3464980889</v>
       </c>
       <c r="F58" s="123">
-        <v>2342190.8283860921</v>
+        <v>6880827.3159572938</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16601,19 +16600,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>1908926.1221606743</v>
+        <v>5607993.5273926323</v>
       </c>
       <c r="C59" s="341">
-        <v>2040259.1412912107</v>
+        <v>5993820.2561836503</v>
       </c>
       <c r="D59" s="123">
-        <v>2186218.9744382254</v>
+        <v>6422617.2588781724</v>
       </c>
       <c r="E59" s="123">
-        <v>2348719.9246601746</v>
+        <v>6900008.3252272233</v>
       </c>
       <c r="F59" s="123">
-        <v>2529935.9203610597</v>
+        <v>7432379.9655714268</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16632,19 +16631,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>1908926.1221606741</v>
+        <v>5607993.5273926323</v>
       </c>
       <c r="C60" s="341">
-        <v>2072357.9267985765</v>
+        <v>6088119.233641576</v>
       </c>
       <c r="D60" s="123">
-        <v>2258526.0635502022</v>
+        <v>6635039.1452032421</v>
       </c>
       <c r="E60" s="123">
-        <v>2471213.5598407467</v>
+        <v>7259866.9416842647</v>
       </c>
       <c r="F60" s="123">
-        <v>2714871.2229095367</v>
+        <v>7975678.0888661984</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16663,19 +16662,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>1908926.1221606741</v>
+        <v>5607993.5273926333</v>
       </c>
       <c r="C61" s="341">
-        <v>2099905.1955445241</v>
+        <v>6169046.883502516</v>
       </c>
       <c r="D61" s="123">
-        <v>2322310.9746544929</v>
+        <v>6822424.7985638324</v>
       </c>
       <c r="E61" s="123">
-        <v>2582465.0238119797</v>
+        <v>7586698.5998719856</v>
       </c>
       <c r="F61" s="123">
-        <v>2888064.7726843893</v>
+        <v>8484481.5961617939</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16755,23 +16754,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>0.36792251927912745</v>
+        <v>6.7965000211345696</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>0.36792251927912745</v>
+        <v>6.7965000211345696</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>0.36792251927912745</v>
+        <v>6.7965000211345696</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>0.36792251927912745</v>
+        <v>6.7965000211345696</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>0.36792251927912745</v>
+        <v>6.7965000211345696</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16782,23 +16781,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>0.36792251927912706</v>
+        <v>6.7965000211345679</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>0.42062966265020385</v>
+        <v>6.9513416964833183</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>0.47411479711318433</v>
+        <v>7.1084689338331968</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>0.5283949682253043</v>
+        <v>7.2679318091790392</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>0.58348748732792033</v>
+        <v>7.4297811793293773</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16809,23 +16808,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>0.36792251927912623</v>
+        <v>6.7965000211345661</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>0.47165051914120798</v>
+        <v>7.1012294420812037</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>0.58040486125410218</v>
+        <v>7.4207251206015625</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>0.69447928214546018</v>
+        <v>7.7558499882290732</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>0.81418368707432143</v>
+        <v>8.1075144765758598</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16836,23 +16835,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>0.36792251927912584</v>
+        <v>6.7965000211345661</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>0.5332331138985783</v>
+        <v>7.2821451877405883</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>0.71196828710161209</v>
+        <v>7.8072287322548677</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>0.90540104330624527</v>
+        <v>8.3754904539570489</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>1.1149254392147148</v>
+        <v>8.9910257763798924</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16863,23 +16862,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>0.36792251927912584</v>
+        <v>6.7965000211345643</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>0.59435718465762744</v>
+        <v>7.4617138935198586</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>0.84601031953680284</v>
+        <v>8.201013929894815</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>1.1261824234813786</v>
+        <v>9.0240962520638597</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>1.4386216228496442</v>
+        <v>9.941972008186756</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16890,23 +16889,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>0.36792251927912539</v>
+        <v>6.7965000211345643</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>0.64969953347085674</v>
+        <v>7.6242972068981736</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>0.97067684769519713</v>
+        <v>8.5672560148443697</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>1.3373768776767894</v>
+        <v>9.6445378282986258</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>1.7574733756416407</v>
+        <v>10.878686397024069</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16916,23 +16915,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>0.36792251927912539</v>
+        <v>6.7965000211345661</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>0.6971944941583933</v>
+        <v>7.76382666748201</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>1.0806500676646706</v>
+        <v>8.890332481039545</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>1.5291884128411199</v>
+        <v>10.208036768982236</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>2.0560808678672209</v>
+        <v>11.755927723543595</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16967,7 +16966,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>0.81418368707432143</v>
+        <v>8.1075144765758598</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16989,7 +16988,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>0.5283949682253043</v>
+        <v>7.2679318091790392</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17012,7 +17011,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>0.47411479711318433</v>
+        <v>7.1084689338331968</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17035,7 +17034,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>0.42062966265020385</v>
+        <v>6.9513416964833183</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17058,7 +17057,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>0.36792251927912623</v>
+        <v>6.7965000211345661</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -18729,7 +18728,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>0.8859517343163833</v>
+        <v>7.5432431801746711</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18785,7 +18784,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>152714.08977285403</v>
+        <v>448639.48219141085</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -18935,7 +18934,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>0.36792251927912745</v>
+        <v>6.7965000211345696</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18982,7 +18981,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>0.47411479711318433</v>
+        <v>7.1084689338331968</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -19040,7 +19039,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>0.42062966265020385</v>
+        <v>6.9513416964833183</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19098,7 +19097,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>0.5283949682253043</v>
+        <v>7.2679318091790392</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19125,7 +19124,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>0.47427380444301215</v>
+        <v>7.1089360614323898</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19199,7 +19198,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>0.36792251927912623</v>
+        <v>6.7965000211345661</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19257,7 +19256,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>0.81418368707432143</v>
+        <v>8.1075144765758598</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19283,7 +19282,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>0.48595173431638328</v>
+        <v>7.1432431801746707</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19345,7 +19344,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>0.49438996007807068</v>
+        <v>7.1680327804137081</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19408,7 +19407,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-6.0156314375584747</v>
+        <v>-0.40211246234825659</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19480,7 +19479,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>0.19751124699136643</v>
+        <v>2.9033148118374918</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19490,7 +19489,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>0.87586312424585011</v>
+        <v>3.5816666890919757</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19501,7 +19500,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>-0.80236649526105297</v>
+        <v>0.49859376213979112</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19531,7 +19530,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-0.43709190940773135</v>
+        <v>6.6775026397374759E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19569,7 +19568,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>0.24880728796998824</v>
+        <v>3.6573405082494315</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19579,7 +19578,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>1.0296072879699882</v>
+        <v>4.4381405082494316</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19590,7 +19589,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>-1.1187439312638672</v>
+        <v>0.3786939074723048</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19629,7 +19628,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>0.38576415428001259</v>
+        <v>5.6705367418701016</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19641,7 +19640,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>1.4166029491791647</v>
+        <v>6.7013755367692536</v>
       </c>
       <c r="D99" t="s">
         <v>395</v>
@@ -19651,7 +19650,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>-1.9151103888372432</v>
+        <v>6.1858126940403602E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19687,7 +19686,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>0.34589084587707208</v>
+        <v>5.0844194009761843</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19697,7 +19696,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>1.3066233531657026</v>
+        <v>6.0451519082648151</v>
       </c>
       <c r="D105" t="s">
         <v>395</v>
@@ -19707,7 +19706,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>-1.6429002582483059</v>
+        <v>0.15665119099582092</v>
       </c>
     </row>
     <row r="106" spans="2:8">
